--- a/haklaut/menu-dev.xlsx
+++ b/haklaut/menu-dev.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/haklaut/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44E7FB85-F76D-487A-AC90-72AD12F982A5}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B85440C1-4958-40BF-BC57-18039048348E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
   <si>
     <t>page_name</t>
   </si>
@@ -247,6 +247,21 @@
   </si>
   <si>
     <t>https://bagruyot.org/haklaut/susim/hitnahagut.html</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/susim/imag/levicon.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/susim/imag/hamlata.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/susim/imag/tolaim.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/susim/imag/tzuna.png</t>
+  </si>
+  <si>
+    <t>https://bagruyot.org/haklaut/susim/imag/hushim.png</t>
   </si>
 </sst>
 </file>
@@ -865,8 +880,8 @@
       <c r="B15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C15" t="s">
-        <v>58</v>
+      <c r="C15" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="D15" t="s">
         <v>59</v>
@@ -876,11 +891,11 @@
       <c r="A16" t="s">
         <v>61</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C16" t="s">
-        <v>58</v>
+      <c r="C16" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="D16" t="s">
         <v>59</v>
@@ -893,8 +908,8 @@
       <c r="B17" t="s">
         <v>64</v>
       </c>
-      <c r="C17" t="s">
-        <v>58</v>
+      <c r="C17" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="D17" t="s">
         <v>59</v>
@@ -907,8 +922,8 @@
       <c r="B18" t="s">
         <v>67</v>
       </c>
-      <c r="C18" t="s">
-        <v>58</v>
+      <c r="C18" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="D18" t="s">
         <v>59</v>
@@ -921,8 +936,8 @@
       <c r="B19" t="s">
         <v>69</v>
       </c>
-      <c r="C19" t="s">
-        <v>58</v>
+      <c r="C19" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="D19" t="s">
         <v>59</v>
@@ -953,6 +968,12 @@
     <hyperlink ref="C14" r:id="rId21" xr:uid="{911EC805-60C2-4E6A-8C4A-33407EAE8CF4}"/>
     <hyperlink ref="B14" r:id="rId22" display="https://tanyatabakmaher.github.io/haklaut/klavim/lemida.html" xr:uid="{EBC0AA92-E021-497F-B4EA-CF4C1550338B}"/>
     <hyperlink ref="B15" r:id="rId23" xr:uid="{3264DF2F-DD71-4D02-91C5-A8C96F628C72}"/>
+    <hyperlink ref="B16" r:id="rId24" xr:uid="{3FB72D6C-A167-4E8E-A9AC-B0B8E58BF8CA}"/>
+    <hyperlink ref="C15" r:id="rId25" xr:uid="{18402C66-CAC9-4D5D-A8B0-4B524490A0A5}"/>
+    <hyperlink ref="C16" r:id="rId26" xr:uid="{44EEF754-3F8D-4E08-BE13-CACA382C642B}"/>
+    <hyperlink ref="C17" r:id="rId27" xr:uid="{5C7B5FE1-8424-41C4-A01D-54303D394D74}"/>
+    <hyperlink ref="C18" r:id="rId28" xr:uid="{0A3C0909-42D1-42B3-A092-3146A59580FD}"/>
+    <hyperlink ref="C19" r:id="rId29" xr:uid="{0B46E610-5DC5-477F-8DAB-8049C0DE66B0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/haklaut/menu-dev.xlsx
+++ b/haklaut/menu-dev.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/haklaut/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B85440C1-4958-40BF-BC57-18039048348E}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63449CEE-847D-42B3-9CD6-5A73A3656F07}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="80">
   <si>
     <t>page_name</t>
   </si>
@@ -262,6 +262,21 @@
   </si>
   <si>
     <t>https://bagruyot.org/haklaut/susim/imag/hushim.png</t>
+  </si>
+  <si>
+    <t>מערכת הדם, תפקידי הלב וכלי הדם, מדדי בריאות בסיסיים, חיסונים, נוגדנים וזיכרון חיסוני בסוסים.</t>
+  </si>
+  <si>
+    <t>השבחה גנטית, בדיקת הריון, שלבי ההריון, תהליך ההמלטה, טיפול בסייח וזיהוי מצבי סיכון.</t>
+  </si>
+  <si>
+    <t>מחלות נפוצות בסוסים, טפילים, מניעה וטיפול, ממשק תברואה, עזרה ראשונה וכללי הזנה במצבי מחלה.</t>
+  </si>
+  <si>
+    <t>מזון גס ומרוכז, סוגי מזון, חציר ושחת, בעיות הזנה, אנומליות אכילה ושגרת שתייה בסוסים.</t>
+  </si>
+  <si>
+    <t>חמשת החושים, התנהגות טבעית, שינה ומנוחה, תקשורת, פחד ותגובות, היררכיה ויחסים בתוך הקבוצה.</t>
   </si>
 </sst>
 </file>
@@ -627,15 +642,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026AC43-3F7F-45AF-806E-B0659676E60E}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
-    <col min="2" max="2" width="25.875" customWidth="1"/>
-    <col min="3" max="3" width="29.625" customWidth="1"/>
-    <col min="4" max="4" width="18.125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="29.58203125" customWidth="1"/>
+    <col min="4" max="4" width="18.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -652,7 +667,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -669,7 +684,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -686,7 +701,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -703,7 +718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -720,7 +735,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -737,7 +752,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -754,7 +769,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -771,7 +786,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -788,7 +803,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -805,7 +820,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -822,7 +837,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -839,7 +854,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -856,7 +871,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -873,7 +888,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>65</v>
       </c>
@@ -886,8 +901,11 @@
       <c r="D15" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -900,8 +918,11 @@
       <c r="D16" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -914,8 +935,11 @@
       <c r="D17" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -928,8 +952,11 @@
       <c r="D18" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>68</v>
       </c>
@@ -941,6 +968,9 @@
       </c>
       <c r="D19" t="s">
         <v>59</v>
+      </c>
+      <c r="E19" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
